--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:47+00:00</t>
+    <t>2026-04-24T09:43:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T09:43:59+00:00</t>
+    <t>2026-04-27T07:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:59:40+00:00</t>
+    <t>2026-04-29T12:03:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T12:03:21+00:00</t>
+    <t>2026-04-30T08:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:28:21+00:00</t>
+    <t>2026-05-12T12:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T12:09:12+00:00</t>
+    <t>2026-05-13T09:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T09:55:21+00:00</t>
+    <t>2026-05-13T11:02:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T11:02:09+00:00</t>
+    <t>2026-05-13T12:39:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T12:39:13+00:00</t>
+    <t>2026-05-13T13:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T13:10:24+00:00</t>
+    <t>2026-05-18T13:11:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T13:11:08+00:00</t>
+    <t>2026-05-18T13:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T13:17:12+00:00</t>
+    <t>2026-05-18T14:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:00:34+00:00</t>
+    <t>2026-05-18T14:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:12:30+00:00</t>
+    <t>2026-05-21T09:30:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:30:02+00:00</t>
+    <t>2026-05-28T09:26:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T09:26:44+00:00</t>
+    <t>2026-06-08T09:06:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
+++ b/464-ajout-des-url-des-jdv-nos-dans-lot23/ig/StructureDefinition-tddui-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:06:06+00:00</t>
+    <t>2026-06-08T13:38:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
